--- a/docs/deliverables/coordinator_dynamic_scheme/Coordinator_Complete_Dynamic_Scheme.xlsx
+++ b/docs/deliverables/coordinator_dynamic_scheme/Coordinator_Complete_Dynamic_Scheme.xlsx
@@ -811,10 +811,10 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1. ★★ DEVIANCE_LEVEL_APPLIED (Task Ledger, Match Log) — the confirmed universal rule ('the +1/0/-1/-2/-3 rule shall come into play') had a Deviance Policy table defining the ladder, but no field anywhere recorded which exact rung a given booking actually used — only a free-text match_score percentage that couldn't be reliably mapped back to it. Added as a real integer field on both Task Ledger and Match Log.</t>
+          <t>1. ★★ DEVIANCE_LEVEL_APPLIED (Task Ledger, Match Log) — the confirmed universal rule ('the -3..+3 symmetric deviance rule shall come into play') had a Deviance Policy table defining the ladder, but no field anywhere recorded which exact rung a given booking actually used — only a free-text match_score percentage that couldn't be reliably mapped back to it. Added as a real integer field on both Task Ledger and Match Log.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>10. Admin Policies — Compliance Policy, Deviance Policy (full +1/0/-1/-2/-3 ladder), Job Tier Master (real Regular/Premium/Platinum names), Trade Master.</t>
+          <t>10. Admin Policies — Compliance Policy, Deviance Policy (full -3..+3 symmetric ladder, 0-5 skill-grade basis), Job Tier Master (real Regular/Premium/Platinum names), Trade Master.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1888,7 +1888,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>10B — DEVIANCE POLICY (the full +1/0/-1/-2/-3 ladder)</t>
+          <t>10B-i — SKILL GRADE SCALE (★★★★ fourth review pass — the real basis the ±3 ladder is derived from)</t>
         </is>
       </c>
     </row>
@@ -1917,315 +1917,230 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>0–5. 0 = not yet assessed/not applicable. 1 is the floor — no worker is onboarded below grade 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>grade_label</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>0 N/A, 1–2 Regular, 3 Premium, 4–5 Platinum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>tier_floor_for</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Which Job Tier this grade is the MINIMUM admissible floor for, if any.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>grade_label</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>tier_floor_for</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Not Applicable / Not Yet Assessed</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Regular (floor — minimum onboarding admittance)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Regular floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Premium (floor)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Premium floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Platinum (floor)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Platinum floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Platinum (specialist)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="39" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>This is the real arithmetic the ±3 deviance ladder below is built from — a job's min_proficiency_req is set from its own tier's floor (Regular=1, Premium=3, Platinum=4); a candidate's own grade (1–5) compared against that floor is exactly what deviance_level_applied computes. Confirmed by the project owner directly: 'the numbering is 0 to 5 grading... Platinum is 4 or above, premium is 3... it can go up to -3 and likewise up to +3.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>10B-ii — DEVIANCE POLICY (★★★★ the full symmetric -3..+3 ladder, corrected walk order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
           <t>policy_id</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>Unique row id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>applies_to_trade</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>FK or 'ALL'</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>A specific trade, or ALL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>applies_to_tier</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>FK or 'ALL'</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>A specific job tier, or ALL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>deviance_level</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr"/>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>+1 (above required), 0 (exact), -1, -2, -3 (below required).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>AUTO_BOOK / ASK_COORDINATOR / NOT_ALLOWED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>policy_id</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>trade</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>deviance</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-01</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>AUTO_BOOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-02</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>AUTO_BOOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-03</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E29" s="29" t="inlineStr">
-        <is>
-          <t>ASK_COORDINATOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-04</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E30" s="29" t="inlineStr">
-        <is>
-          <t>ASK_COORDINATOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-05</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>ASK_COORDINATOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>POL-D-06</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>SUPERVISOR</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>NOT_ALLOWED</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>10C — JOB TIER MASTER (★★★ real tier names: Regular / Premium / Platinum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Field Name</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>tier_id</t>
+          <t>applies_to_trade</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -2235,19 +2150,19 @@
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>FK or 'ALL'</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>Unique row id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="39" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>tier_name</t>
+          <t>A specific trade, or ALL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>applies_to_tier</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -2255,17 +2170,21 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr"/>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>FK or 'ALL'</t>
+        </is>
+      </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>Regular / Premium / Platinum — the real 3 levels a client picks at estimate time, each with its own matching rate card. This is also the fixed priority order for every deployment/redeployment decision: Platinum &gt; Premium &gt; Regular.</t>
+          <t>A specific job tier, or ALL.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>priority_rank</t>
+          <t>deviance_level</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -2276,301 +2195,659 @@
       <c r="C39" s="20" t="inlineStr"/>
       <c r="D39" s="21" t="inlineStr">
         <is>
+          <t>-3 to +3, symmetric around 0 (exact grade match against the job's own tier floor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>AUTO_BOOK / ASK_COORDINATOR / NOT_ALLOWED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>WALK ORDER — confirmed, and a real correction from this pass's earlier draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>The negative (lower-standard, cheaper-substitute) side is walked FIRST and FULLY: 0 → -1 → -2 → -3 — 'the trigger is to judge none is available even by lowering standards... a preference in regular/premium class for economy of business sense of Project.' Only once the entire negative side is exhausted does the engine fall back to the positive (over-qualified, costlier) side, in order: +1 → +2 → +3. This REVERSES an earlier draft of this same ladder, which checked +1 immediately after 0, before any negative level — corrected here because an over-qualified substitute has a real cost impact the earlier draft didn't account for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>policy_id</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>deviance</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-00</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>AUTO_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-N1</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>AUTO_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-N2</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>ASK_COORDINATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-N3</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>ASK_COORDINATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-P1</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>AUTO_BOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-P2</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t>ASK_COORDINATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-P3</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>ASK_COORDINATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>POL-D-06</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
+        <is>
+          <t>NOT_ALLOWED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="39" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>ACTION COLUMN IS A PROPOSED DEFAULT, NOT YET OWNER-CONFIRMED: 0 and the first step each direction (-1, +1) auto-book; the deeper steps each direction (-2/-3, +2/+3) ask the Coordinator, since both a bigger standards-drop and a bigger cost jump deserve a conscious nod rather than a silent auto-book. Flagged here exactly as such — correct per-row if this default doesn't match intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>10C — JOB TIER MASTER (★★★ real tier names: Regular / Premium / Platinum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>tier_id</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>Unique row id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="39" customHeight="1">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>tier_name</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr"/>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Regular / Premium / Platinum — the real 3 levels a client picks at estimate time, each with its own matching rate card. This is also the fixed priority order for every deployment/redeployment decision: Platinum &gt; Premium &gt; Regular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>priority_rank</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr"/>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
           <t>Lower = higher priority. Platinum = 1 (highest).</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>tier_id</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>tier_name</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>priority_rank</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>T-1</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C42" s="24" t="n">
+      <c r="C63" s="24" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>T-2</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="C43" s="24" t="n">
+      <c r="C64" s="24" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>T-3</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C65" s="24" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>10D — TRADE MASTER</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>trade_code</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D49" s="21" t="inlineStr">
+      <c r="D70" s="21" t="inlineStr">
         <is>
           <t>e.g. MASON.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>trade_name</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr"/>
-      <c r="D50" s="21" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr"/>
+      <c r="D71" s="21" t="inlineStr">
         <is>
           <t>Display name.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="22" t="inlineStr">
         <is>
           <t>skill_bucket</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr"/>
-      <c r="D51" s="21" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr"/>
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>Skilled / Semi-Skilled / Unskilled.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>trade_code</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>trade_name</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>skill_bucket</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>MASON</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>Mason</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>Skilled</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>PLUMBER</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>Plumber</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>Skilled</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>ELECTRICIAN</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>Electrician</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>Skilled</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>WATERPROOFER</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B78" s="16" t="inlineStr">
         <is>
           <t>Waterproofer</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>Skilled</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>TILER</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>Tiler</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C79" s="16" t="inlineStr">
         <is>
           <t>Skilled</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B80" s="16" t="inlineStr">
         <is>
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>Highly Skilled</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>HELPER</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>Helper</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>Unskilled</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A47:E47"/>
+  <mergeCells count="11">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -4449,12 +4726,12 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>The +1/0/-1/-2/-3 proficiency tolerance ladder, per trade/tier.</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>The -3..+3 symmetric proficiency tolerance ladder, per trade/tier.</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>★★★★ full ±3 ladder + corrected negative-first walk order</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6750,7 @@
       <c r="C23" s="20" t="inlineStr"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>+1 / 0 / -1 / -2 / -3, from the Deviance Policy ladder — the confirmed universal rule ('the +1/0/-1/-2/-3 rule shall come into play') had no actual field recording which rung was used on a given booking until this pass; match_score alone (a percentage string) couldn't be reliably mapped back to it.</t>
+          <t>-3 to +3, symmetric, from the Deviance Policy ladder — walked negative-side-first (0 -&gt; -1 -&gt; -2 -&gt; -3 for cost economy) then positive-side as a last resort (+1 -&gt; +2 -&gt; +3) before NO SUPPLY. match_score alone (a percentage string) couldn't be reliably mapped back to the exact rung used; this field is the real record.</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10559,7 @@
     <row r="3" ht="39" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>One row per candidate actually considered for a slot — the algorithm's own audit trail, feeding the summary match_score now also shown directly on the Task Ledger. deviance_level_applied added this pass — the confirmed +1/0/-1/-2/-3 ladder had no field recording which exact rung a candidate sat on, only a free-text percentage.</t>
+          <t>One row per candidate actually considered for a slot — the algorithm's own audit trail, feeding the summary match_score now also shown directly on the Task Ledger. deviance_level_applied added this pass — the confirmed -3..+3 symmetric ladder had no field recording which exact rung a candidate sat on, only a free-text percentage.</t>
         </is>
       </c>
     </row>
